--- a/bindings/excel/examples/interpolation_example.xlsx
+++ b/bindings/excel/examples/interpolation_example.xlsx
@@ -4,16 +4,159 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" r:id="rId1"/>
-    <sheet name="One Dimension" sheetId="2" r:id="rId2"/>
-    <sheet name="Two Dimensions" sheetId="3" r:id="rId3"/>
-    <sheet name="Schedules" sheetId="4" r:id="rId4"/>
+    <sheet name="Start Here" sheetId="1" r:id="rId1"/>
+    <sheet name="1 Inputs" sheetId="2" r:id="rId2"/>
+    <sheet name="2 Interpolation" sheetId="3" r:id="rId3"/>
+    <sheet name="3 Schedules" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="Interpolation_Analytic">'2 Interpolation'!$B$19</definedName>
+    <definedName name="Interpolation_B10">'2 Interpolation'!$B$10</definedName>
+    <definedName name="Interpolation_B11">'2 Interpolation'!$B$11</definedName>
+    <definedName name="Interpolation_B12">'2 Interpolation'!$B$12</definedName>
+    <definedName name="Interpolation_B13">'2 Interpolation'!$B$13</definedName>
+    <definedName name="Interpolation_B7">'2 Interpolation'!$B$7</definedName>
+    <definedName name="Interpolation_B8">'2 Interpolation'!$B$8</definedName>
+    <definedName name="Interpolation_B9">'2 Interpolation'!$B$9</definedName>
+    <definedName name="Interpolation_Bilinear">'2 Interpolation'!$B$18</definedName>
+    <definedName name="Interpolation_C10">'2 Interpolation'!$C$10</definedName>
+    <definedName name="Interpolation_C11">'2 Interpolation'!$C$11</definedName>
+    <definedName name="Interpolation_C12">'2 Interpolation'!$C$12</definedName>
+    <definedName name="Interpolation_C13">'2 Interpolation'!$C$13</definedName>
+    <definedName name="Interpolation_C7">'2 Interpolation'!$C$7</definedName>
+    <definedName name="Interpolation_C8">'2 Interpolation'!$C$8</definedName>
+    <definedName name="Interpolation_C9">'2 Interpolation'!$C$9</definedName>
+    <definedName name="Interpolation_Calendar">'1 Inputs'!$B$38</definedName>
+    <definedName name="Interpolation_Convention">'1 Inputs'!$B$39</definedName>
+    <definedName name="Interpolation_D10">'2 Interpolation'!$D$10</definedName>
+    <definedName name="Interpolation_D11">'2 Interpolation'!$D$11</definedName>
+    <definedName name="Interpolation_D12">'2 Interpolation'!$D$12</definedName>
+    <definedName name="Interpolation_D13">'2 Interpolation'!$D$13</definedName>
+    <definedName name="Interpolation_D7">'2 Interpolation'!$D$7</definedName>
+    <definedName name="Interpolation_D8">'2 Interpolation'!$D$8</definedName>
+    <definedName name="Interpolation_D9">'2 Interpolation'!$D$9</definedName>
+    <definedName name="Interpolation_Difference">'2 Interpolation'!$B$20</definedName>
+    <definedName name="Interpolation_End">'1 Inputs'!$B$36</definedName>
+    <definedName name="Interpolation_Factors">'1 Inputs'!$B$7:$B$11</definedName>
+    <definedName name="Interpolation_Frequency">'1 Inputs'!$B$37</definedName>
+    <definedName name="Interpolation_QueryX">'1 Inputs'!$B$31</definedName>
+    <definedName name="Interpolation_QueryY">'1 Inputs'!$B$32</definedName>
+    <definedName name="Interpolation_Start">'1 Inputs'!$B$35</definedName>
+    <definedName name="Interpolation_SurfaceValues">'1 Inputs'!$C$25:$C$28</definedName>
+    <definedName name="Interpolation_SurfaceX">'1 Inputs'!$A$25:$A$28</definedName>
+    <definedName name="Interpolation_SurfaceY">'1 Inputs'!$B$25:$B$28</definedName>
+    <definedName name="Interpolation_Times">'1 Inputs'!$A$7:$A$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Start Here'!$A$1:$F$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'1 Inputs'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'2 Interpolation'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'3 Schedules'!$1:$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="B31" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Used by the corresponding result tab.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B32" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Used by the corresponding result tab.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B35" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Used by the corresponding result tab.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B36" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Used by the corresponding result tab.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B37" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Used by the corresponding result tab.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B38" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Used by the corresponding result tab.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B39" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Used by the corresponding result tab.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
@@ -39,30 +182,93 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
-  <si>
-    <t>Interpolation and schedules: nodes, methods, and worksheet layouts</t>
-  </si>
-  <si>
-    <t>Load quantsupport.xll in 64-bit Windows Excel, then open this workbook and press Ctrl+Alt+F9.</t>
-  </si>
-  <si>
-    <t>Blue cells are editable inputs. Rates and spreads are annual decimals; dates are ISO text.</t>
-  </si>
-  <si>
-    <t>Compare linear, log-linear, and natural cubic-spline interpolation on a positive discount-factor grid.</t>
-  </si>
-  <si>
-    <t>The two-dimensional example reproduces a surface with an x*y interaction at nodes and between them.</t>
-  </si>
-  <si>
-    <t>Schedules compares unadjusted and TARGET-adjusted dates; lists can be transposed directly.</t>
-  </si>
-  <si>
-    <t>These are illustrative assumptions, following the questions explored in the Python notebook studies.</t>
-  </si>
-  <si>
-    <t>Table functions end with transpose,headers. Defaults are FALSE,TRUE; TRUE,FALSE transposes without headers.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="64">
+  <si>
+    <t>Interpolation and schedules · see what changes</t>
+  </si>
+  <si>
+    <t>Compare three native one-dimensional methods, verify a bilinear surface, then inspect date-list layouts.</t>
+  </si>
+  <si>
+    <t>Before you start: load quantsupport.xll in 64-bit Windows Excel, then press Ctrl+Alt+F9. Results are blank until Excel calculates. Dates are ISO text; enter 4% as 0.04.</t>
+  </si>
+  <si>
+    <t>Follow the numbered tabs from left to right</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>1 Inputs</t>
+  </si>
+  <si>
+    <t>Edit curve nodes, query points, surface coordinates and dates.</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>2 Interpolation</t>
+  </si>
+  <si>
+    <t>Compare methods and check the bilinear example.</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>3 Schedules</t>
+  </si>
+  <si>
+    <t>Compare unadjusted, adjusted and transposed date lists.</t>
+  </si>
+  <si>
+    <t>Cell colours</t>
+  </si>
+  <si>
+    <t>Blue · edit</t>
+  </si>
+  <si>
+    <t>Assumptions and choices you can change.</t>
+  </si>
+  <si>
+    <t>Green · read</t>
+  </si>
+  <si>
+    <t>Financial results calculated by the add-in.</t>
+  </si>
+  <si>
+    <t>Grey · build</t>
+  </si>
+  <si>
+    <t>Object references on the Build tab. Each step shows its Excel formula below.</t>
+  </si>
+  <si>
+    <t>Try this first</t>
+  </si>
+  <si>
+    <t>1. Change one positive discount-factor node and compare the three methods.</t>
+  </si>
+  <si>
+    <t>2. Move the bilinear query and compare the native and analytic values.</t>
+  </si>
+  <si>
+    <t>3. Compare the same schedule before and after TARGET / Following adjustment.</t>
+  </si>
+  <si>
+    <t>Use Ctrl+A after a function name for parameter help. Inline hints use the optional Excel-DNA IntelliSense companion. The example assumptions are illustrative; tables and results use the native Rust pricers.</t>
+  </si>
+  <si>
+    <t>Numerical inputs</t>
+  </si>
+  <si>
+    <t>Blue cells are editable. Positive discount factors support log-linear interpolation. The bilinear surface is 2 + x + 3y + xy.</t>
+  </si>
+  <si>
+    <t>← Start Here</t>
+  </si>
+  <si>
+    <t>Next → 2 Interpolation</t>
   </si>
   <si>
     <t>Time</t>
@@ -71,7 +277,64 @@
     <t>Discount factor</t>
   </si>
   <si>
-    <t>Query</t>
+    <t>Query point</t>
+  </si>
+  <si>
+    <t>Surface x</t>
+  </si>
+  <si>
+    <t>Surface y</t>
+  </si>
+  <si>
+    <t>Surface value</t>
+  </si>
+  <si>
+    <t>Query x</t>
+  </si>
+  <si>
+    <t>Used by the corresponding result tab.</t>
+  </si>
+  <si>
+    <t>Query y</t>
+  </si>
+  <si>
+    <t>Schedule start</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>Schedule end</t>
+  </si>
+  <si>
+    <t>2027-02-28</t>
+  </si>
+  <si>
+    <t>Frequency</t>
+  </si>
+  <si>
+    <t>Quarterly</t>
+  </si>
+  <si>
+    <t>Calendar</t>
+  </si>
+  <si>
+    <t>TARGET</t>
+  </si>
+  <si>
+    <t>Business-day convention</t>
+  </si>
+  <si>
+    <t>Following</t>
+  </si>
+  <si>
+    <t>Compare native interpolation methods</t>
+  </si>
+  <si>
+    <t>The same nodes feed all three methods. Query points must stay inside the node range because extrapolation is disabled.</t>
+  </si>
+  <si>
+    <t>Next → 3 Schedules</t>
   </si>
   <si>
     <t>Linear</t>
@@ -83,44 +346,46 @@
     <t>Cubic spline</t>
   </si>
   <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
-    <t>2 + x + 3*y + x*y</t>
-  </si>
-  <si>
-    <t>Query x</t>
-  </si>
-  <si>
-    <t>Query y</t>
-  </si>
-  <si>
-    <t>Native bilinear</t>
+    <t>Bilinear surface</t>
+  </si>
+  <si>
+    <t>Calculated value</t>
+  </si>
+  <si>
+    <t>Native interpolation</t>
   </si>
   <si>
     <t>Analytic value</t>
   </si>
   <si>
-    <t>Unadjusted quarterly dates</t>
-  </si>
-  <si>
-    <t>Same dates transposed</t>
-  </si>
-  <si>
-    <t>Following TARGET adjustment</t>
+    <t>Difference</t>
+  </si>
+  <si>
+    <t>The same schedule in different layouts</t>
+  </si>
+  <si>
+    <t>Both date columns use the same start, end and frequency. The adjusted list adds TARGET / Following. Lists have no headers; transpose changes orientation only.</t>
+  </si>
+  <si>
+    <t>Unadjusted</t>
+  </si>
+  <si>
+    <t>TARGET / Following</t>
+  </si>
+  <si>
+    <t>The unadjusted list transposed into one row</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000000"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,9 +394,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF273B4A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="20"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF526779"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF17324D"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -145,15 +432,48 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF003070"/>
+      <color rgb="FF126B9A"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF526779"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF174EA6"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF145C43"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF526779"/>
+      <name val="Consolas"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -162,30 +482,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF003070"/>
+        <fgColor rgb="FF17324D"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2C5AA0"/>
+        <fgColor rgb="FFE5EDF2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD6E4FC"/>
+        <fgColor rgb="FF176B75"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCFD9E8"/>
+        <fgColor rgb="FFE8F1FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF5EF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F2F5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -194,17 +526,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FFCBDBEE"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FFCBDBEE"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FFCBDBEE"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FFCBDBEE"/>
       </bottom>
       <diagonal/>
     </border>
@@ -212,25 +553,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -239,6 +601,377 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Same nodes · different interpolation</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Linear</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="176B75"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="4"/>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>'2 Interpolation'!$A$7:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v/>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'2 Interpolation'!$B$7:$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Log-linear</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="337AB7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="4"/>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>'2 Interpolation'!$A$7:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v/>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'2 Interpolation'!$C$7:$C$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Cubic spline</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B27C2C"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="4"/>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>'2 Interpolation'!$A$7:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v/>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'2 Interpolation'!$D$7:$D$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:axId val="50010001"/>
+        <c:axId val="50010002"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="50010001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Time</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50010002"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="50010002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Discount factor</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50010001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1247775</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -526,14 +1259,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultRowHeight="26" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="115.7109375" style="1" customWidth="1"/>
-    <col min="2" max="12" width="22.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="1" customWidth="1"/>
+    <col min="4" max="5" width="22.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" customHeight="1">
+    <row r="1" spans="1:6" ht="30" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -543,367 +1282,853 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="4" spans="1:6" ht="34" customHeight="1">
-      <c r="A4" s="1" t="s">
+    <row r="2" spans="1:6" ht="30" customHeight="1">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" ht="26" customHeight="1">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="34" customHeight="1">
-      <c r="A5" s="1" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="1:6" ht="26" customHeight="1">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="6" spans="1:6" ht="26" customHeight="1">
+      <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="34" customHeight="1">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" ht="26" customHeight="1">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="9" spans="1:6" ht="26" customHeight="1">
+      <c r="A9" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="34" customHeight="1">
-      <c r="A7" s="1" t="s">
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+    </row>
+    <row r="10" spans="1:6" ht="34" customHeight="1">
+      <c r="A10" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="34" customHeight="1">
-      <c r="A8" s="1" t="s">
+      <c r="B10" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="34" customHeight="1">
-      <c r="A9" s="1" t="s">
+      <c r="C10" s="7"/>
+      <c r="D10" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="34" customHeight="1">
-      <c r="A10" s="1" t="s">
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" ht="34" customHeight="1">
+      <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="B11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" ht="34" customHeight="1">
+      <c r="A12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="15" spans="1:6" ht="26" customHeight="1">
+      <c r="A15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+    </row>
+    <row r="16" spans="1:6" ht="30" customHeight="1">
+      <c r="A16" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" ht="30" customHeight="1">
+      <c r="A17" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" ht="30" customHeight="1">
+      <c r="A18" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="20" spans="1:6" ht="26" customHeight="1">
+      <c r="A20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+    </row>
+    <row r="21" spans="1:6" ht="34" customHeight="1">
+      <c r="A21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="1:6" ht="34" customHeight="1">
+      <c r="A22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="1:6" ht="34" customHeight="1">
+      <c r="A23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+    </row>
+    <row r="25" spans="1:6" ht="26" customHeight="1">
+      <c r="A25" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+    </row>
+    <row r="26" spans="1:6" ht="26" customHeight="1">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="22">
+    <mergeCell ref="A1:F2"/>
+    <mergeCell ref="A3:F4"/>
+    <mergeCell ref="A6:F7"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A25:F26"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B10" location="'1 Inputs'!A1" display="1 Inputs"/>
+    <hyperlink ref="B11" location="'2 Interpolation'!A1" display="2 Interpolation"/>
+    <hyperlink ref="B12" location="'3 Schedules'!A1" display="3 Schedules"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A4:L11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr>
+    <tabColor rgb="FF337AB7"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C39"/>
+  <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
-    <col min="1" max="12" width="22.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="32.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:7">
-      <c r="A4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="3" t="s">
+    <row r="1" spans="1:3" ht="38" customHeight="1">
+      <c r="A1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" spans="1:3" ht="24" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" ht="24" customHeight="1">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="1:3" ht="36" customHeight="1">
+      <c r="A4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="36" customHeight="1">
+      <c r="A6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="5"/>
+    </row>
+    <row r="7" spans="1:3" ht="24" customHeight="1">
+      <c r="A7" s="8">
+        <v>0</v>
+      </c>
+      <c r="B7" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="24" customHeight="1">
+      <c r="A8" s="8">
+        <v>1</v>
+      </c>
+      <c r="B8" s="11">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="24" customHeight="1">
+      <c r="A9" s="8">
+        <v>3</v>
+      </c>
+      <c r="B9" s="11">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="24" customHeight="1">
+      <c r="A10" s="8">
+        <v>5</v>
+      </c>
+      <c r="B10" s="11">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="24" customHeight="1">
+      <c r="A11" s="8">
         <v>10</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="4">
+      <c r="B11" s="11">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="36" customHeight="1">
+      <c r="A14" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+    </row>
+    <row r="15" spans="1:3" ht="24" customHeight="1">
+      <c r="A15" s="8">
         <v>0</v>
       </c>
-      <c r="B5" s="4">
+    </row>
+    <row r="16" spans="1:3" ht="24" customHeight="1">
+      <c r="A16" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="24" customHeight="1">
+      <c r="A17" s="8">
         <v>1</v>
       </c>
-      <c r="D5" s="4">
+    </row>
+    <row r="18" spans="1:3" ht="24" customHeight="1">
+      <c r="A18" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="24" customHeight="1">
+      <c r="A19" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="24" customHeight="1">
+      <c r="A20" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="24" customHeight="1">
+      <c r="A21" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="36" customHeight="1">
+      <c r="A24" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="24" customHeight="1">
+      <c r="A25" s="8">
         <v>0</v>
       </c>
-      <c r="E5" s="5" cm="1">
-        <f t="array" ref="E5">_xll.QS.INTERPOLATE.LINEAR(D5,$A$5:$A$9,$B$5:$B$9,FALSE)</f>
+      <c r="B25" s="8">
         <v>0</v>
       </c>
-      <c r="F5" s="5" cm="1">
-        <f t="array" ref="F5">_xll.QS.INTERPOLATE.LOG.LINEAR(D5,$A$5:$A$9,$B$5:$B$9,FALSE)</f>
+      <c r="C25" s="12">
+        <f>2+A25+3*B25+A25*B25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="24" customHeight="1">
+      <c r="A26" s="8">
         <v>0</v>
       </c>
-      <c r="G5" s="5" cm="1">
-        <f t="array" ref="G5">_xll.QS.INTERPOLATE.CUBIC.SPLINE(D5,$A$5:$A$9,$B$5:$B$9,FALSE)</f>
+      <c r="B26" s="8">
+        <v>2</v>
+      </c>
+      <c r="C26" s="12">
+        <f>2+A26+3*B26+A26*B26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="24" customHeight="1">
+      <c r="A27" s="8">
+        <v>1</v>
+      </c>
+      <c r="B27" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="4">
+      <c r="C27" s="12">
+        <f>2+A27+3*B27+A27*B27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="24" customHeight="1">
+      <c r="A28" s="8">
         <v>1</v>
       </c>
-      <c r="B6" s="4">
-        <v>0.97</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="E6" s="5" cm="1">
-        <f t="array" ref="E6">_xll.QS.INTERPOLATE.LINEAR(D6,$A$5:$A$9,$B$5:$B$9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="5" cm="1">
-        <f t="array" ref="F6">_xll.QS.INTERPOLATE.LOG.LINEAR(D6,$A$5:$A$9,$B$5:$B$9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" cm="1">
-        <f t="array" ref="G6">_xll.QS.INTERPOLATE.CUBIC.SPLINE(D6,$A$5:$A$9,$B$5:$B$9,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="4">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0.91</v>
-      </c>
-      <c r="D7" s="4">
-        <v>1</v>
-      </c>
-      <c r="E7" s="5" cm="1">
-        <f t="array" ref="E7">_xll.QS.INTERPOLATE.LINEAR(D7,$A$5:$A$9,$B$5:$B$9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="5" cm="1">
-        <f t="array" ref="F7">_xll.QS.INTERPOLATE.LOG.LINEAR(D7,$A$5:$A$9,$B$5:$B$9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" cm="1">
-        <f t="array" ref="G7">_xll.QS.INTERPOLATE.CUBIC.SPLINE(D7,$A$5:$A$9,$B$5:$B$9,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="4">
-        <v>5</v>
-      </c>
-      <c r="B8" s="4">
-        <v>0.85</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="B28" s="8">
         <v>2</v>
       </c>
-      <c r="E8" s="5" cm="1">
-        <f t="array" ref="E8">_xll.QS.INTERPOLATE.LINEAR(D8,$A$5:$A$9,$B$5:$B$9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="5" cm="1">
-        <f t="array" ref="F8">_xll.QS.INTERPOLATE.LOG.LINEAR(D8,$A$5:$A$9,$B$5:$B$9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="5" cm="1">
-        <f t="array" ref="G8">_xll.QS.INTERPOLATE.CUBIC.SPLINE(D8,$A$5:$A$9,$B$5:$B$9,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="4">
-        <v>10</v>
-      </c>
-      <c r="B9" s="4">
+      <c r="C28" s="12">
+        <f>2+A28+3*B28+A28*B28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="32" customHeight="1">
+      <c r="A31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="32" customHeight="1">
+      <c r="A32" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="8">
         <v>0.7</v>
       </c>
-      <c r="D9" s="4">
-        <v>4</v>
-      </c>
-      <c r="E9" s="5" cm="1">
-        <f t="array" ref="E9">_xll.QS.INTERPOLATE.LINEAR(D9,$A$5:$A$9,$B$5:$B$9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="5" cm="1">
-        <f t="array" ref="F9">_xll.QS.INTERPOLATE.LOG.LINEAR(D9,$A$5:$A$9,$B$5:$B$9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="5" cm="1">
-        <f t="array" ref="G9">_xll.QS.INTERPOLATE.CUBIC.SPLINE(D9,$A$5:$A$9,$B$5:$B$9,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="D10" s="4">
-        <v>7</v>
-      </c>
-      <c r="E10" s="5" cm="1">
-        <f t="array" ref="E10">_xll.QS.INTERPOLATE.LINEAR(D10,$A$5:$A$9,$B$5:$B$9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="5" cm="1">
-        <f t="array" ref="F10">_xll.QS.INTERPOLATE.LOG.LINEAR(D10,$A$5:$A$9,$B$5:$B$9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="5" cm="1">
-        <f t="array" ref="G10">_xll.QS.INTERPOLATE.CUBIC.SPLINE(D10,$A$5:$A$9,$B$5:$B$9,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="D11" s="4">
-        <v>10</v>
-      </c>
-      <c r="E11" s="5" cm="1">
-        <f t="array" ref="E11">_xll.QS.INTERPOLATE.LINEAR(D11,$A$5:$A$9,$B$5:$B$9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="5" cm="1">
-        <f t="array" ref="F11">_xll.QS.INTERPOLATE.LOG.LINEAR(D11,$A$5:$A$9,$B$5:$B$9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="5" cm="1">
-        <f t="array" ref="G11">_xll.QS.INTERPOLATE.CUBIC.SPLINE(D11,$A$5:$A$9,$B$5:$B$9,FALSE)</f>
-        <v>0</v>
+      <c r="C32" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="32" customHeight="1">
+      <c r="A35" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="32" customHeight="1">
+      <c r="A36" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="32" customHeight="1">
+      <c r="A37" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="32" customHeight="1">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="32" customHeight="1">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C3"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here"/>
+    <hyperlink ref="C4" location="'2 Interpolation'!A1" display="Next → 2 Interpolation"/>
+  </hyperlinks>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
+  <headerFooter>
+    <oddFooter>&amp;LQuantSupport&amp;CNumerical inputs&amp;R&amp;P / &amp;N</oddFooter>
+  </headerFooter>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A4:L8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr>
+    <tabColor rgb="FF21845B"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
-    <col min="1" max="12" width="22.7109375" style="1" customWidth="1"/>
+    <col min="1" max="4" width="24.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:8">
-      <c r="A4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="4">
-        <v>0</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0</v>
-      </c>
-      <c r="C5" s="1">
-        <f>2+A5+3*B5+A5*B5</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="G5" s="1" cm="1">
-        <f t="array" ref="G5">_xll.QS.INTERPOLATE.BILINEAR(E5,F5,A5:A8,B5:B8,C5:C8,"Reject")</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="1">
-        <f>2+E5+3*F5+E5*F5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="4">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1">
-        <f>2+A6+3*B6+A6*B6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="4">
-        <v>1</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0</v>
-      </c>
-      <c r="C7" s="1">
-        <f>2+A7+3*B7+A7*B7</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="4">
-        <v>1</v>
-      </c>
-      <c r="B8" s="4">
-        <v>2</v>
-      </c>
-      <c r="C8" s="1">
-        <f>2+A8+3*B8+A8*B8</f>
-        <v>0</v>
+    <row r="1" spans="1:4" ht="38" customHeight="1">
+      <c r="A1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" spans="1:4" ht="24" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="3" spans="1:4" ht="24" customHeight="1">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:4" ht="36" customHeight="1">
+      <c r="A4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="36" customHeight="1">
+      <c r="A6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="24" customHeight="1">
+      <c r="A7" s="12">
+        <f>'1 Inputs'!A15</f>
+        <v/>
+      </c>
+      <c r="B7" s="13" cm="1" t="str">
+        <f t="array" ref="B7">_xll.QS.INTERPOLATE.LINEAR(A7,Interpolation_Times,Interpolation_Factors,FALSE)</f>
+        <v/>
+      </c>
+      <c r="C7" s="13" cm="1" t="str">
+        <f t="array" ref="C7">_xll.QS.INTERPOLATE.LOG.LINEAR(A7,Interpolation_Times,Interpolation_Factors,FALSE)</f>
+        <v/>
+      </c>
+      <c r="D7" s="13" cm="1" t="str">
+        <f t="array" ref="D7">_xll.QS.INTERPOLATE.CUBIC.SPLINE(A7,Interpolation_Times,Interpolation_Factors,FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="24" customHeight="1">
+      <c r="A8" s="12">
+        <f>'1 Inputs'!A16</f>
+        <v/>
+      </c>
+      <c r="B8" s="13" cm="1" t="str">
+        <f t="array" ref="B8">_xll.QS.INTERPOLATE.LINEAR(A8,Interpolation_Times,Interpolation_Factors,FALSE)</f>
+        <v/>
+      </c>
+      <c r="C8" s="13" cm="1" t="str">
+        <f t="array" ref="C8">_xll.QS.INTERPOLATE.LOG.LINEAR(A8,Interpolation_Times,Interpolation_Factors,FALSE)</f>
+        <v/>
+      </c>
+      <c r="D8" s="13" cm="1" t="str">
+        <f t="array" ref="D8">_xll.QS.INTERPOLATE.CUBIC.SPLINE(A8,Interpolation_Times,Interpolation_Factors,FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="24" customHeight="1">
+      <c r="A9" s="12">
+        <f>'1 Inputs'!A17</f>
+        <v/>
+      </c>
+      <c r="B9" s="13" cm="1" t="str">
+        <f t="array" ref="B9">_xll.QS.INTERPOLATE.LINEAR(A9,Interpolation_Times,Interpolation_Factors,FALSE)</f>
+        <v/>
+      </c>
+      <c r="C9" s="13" cm="1" t="str">
+        <f t="array" ref="C9">_xll.QS.INTERPOLATE.LOG.LINEAR(A9,Interpolation_Times,Interpolation_Factors,FALSE)</f>
+        <v/>
+      </c>
+      <c r="D9" s="13" cm="1" t="str">
+        <f t="array" ref="D9">_xll.QS.INTERPOLATE.CUBIC.SPLINE(A9,Interpolation_Times,Interpolation_Factors,FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="24" customHeight="1">
+      <c r="A10" s="12">
+        <f>'1 Inputs'!A18</f>
+        <v/>
+      </c>
+      <c r="B10" s="13" cm="1" t="str">
+        <f t="array" ref="B10">_xll.QS.INTERPOLATE.LINEAR(A10,Interpolation_Times,Interpolation_Factors,FALSE)</f>
+        <v/>
+      </c>
+      <c r="C10" s="13" cm="1" t="str">
+        <f t="array" ref="C10">_xll.QS.INTERPOLATE.LOG.LINEAR(A10,Interpolation_Times,Interpolation_Factors,FALSE)</f>
+        <v/>
+      </c>
+      <c r="D10" s="13" cm="1" t="str">
+        <f t="array" ref="D10">_xll.QS.INTERPOLATE.CUBIC.SPLINE(A10,Interpolation_Times,Interpolation_Factors,FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="24" customHeight="1">
+      <c r="A11" s="12">
+        <f>'1 Inputs'!A19</f>
+        <v/>
+      </c>
+      <c r="B11" s="13" cm="1" t="str">
+        <f t="array" ref="B11">_xll.QS.INTERPOLATE.LINEAR(A11,Interpolation_Times,Interpolation_Factors,FALSE)</f>
+        <v/>
+      </c>
+      <c r="C11" s="13" cm="1" t="str">
+        <f t="array" ref="C11">_xll.QS.INTERPOLATE.LOG.LINEAR(A11,Interpolation_Times,Interpolation_Factors,FALSE)</f>
+        <v/>
+      </c>
+      <c r="D11" s="13" cm="1" t="str">
+        <f t="array" ref="D11">_xll.QS.INTERPOLATE.CUBIC.SPLINE(A11,Interpolation_Times,Interpolation_Factors,FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="24" customHeight="1">
+      <c r="A12" s="12">
+        <f>'1 Inputs'!A20</f>
+        <v/>
+      </c>
+      <c r="B12" s="13" cm="1" t="str">
+        <f t="array" ref="B12">_xll.QS.INTERPOLATE.LINEAR(A12,Interpolation_Times,Interpolation_Factors,FALSE)</f>
+        <v/>
+      </c>
+      <c r="C12" s="13" cm="1" t="str">
+        <f t="array" ref="C12">_xll.QS.INTERPOLATE.LOG.LINEAR(A12,Interpolation_Times,Interpolation_Factors,FALSE)</f>
+        <v/>
+      </c>
+      <c r="D12" s="13" cm="1" t="str">
+        <f t="array" ref="D12">_xll.QS.INTERPOLATE.CUBIC.SPLINE(A12,Interpolation_Times,Interpolation_Factors,FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="24" customHeight="1">
+      <c r="A13" s="12">
+        <f>'1 Inputs'!A21</f>
+        <v/>
+      </c>
+      <c r="B13" s="13" cm="1" t="str">
+        <f t="array" ref="B13">_xll.QS.INTERPOLATE.LINEAR(A13,Interpolation_Times,Interpolation_Factors,FALSE)</f>
+        <v/>
+      </c>
+      <c r="C13" s="13" cm="1" t="str">
+        <f t="array" ref="C13">_xll.QS.INTERPOLATE.LOG.LINEAR(A13,Interpolation_Times,Interpolation_Factors,FALSE)</f>
+        <v/>
+      </c>
+      <c r="D13" s="13" cm="1" t="str">
+        <f t="array" ref="D13">_xll.QS.INTERPOLATE.CUBIC.SPLINE(A13,Interpolation_Times,Interpolation_Factors,FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="36" customHeight="1">
+      <c r="A17" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="1:4" ht="24" customHeight="1">
+      <c r="A18" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="12" cm="1" t="str">
+        <f t="array" ref="B18">_xll.QS.INTERPOLATE.BILINEAR(Interpolation_QueryX,Interpolation_QueryY,Interpolation_SurfaceX,Interpolation_SurfaceY,Interpolation_SurfaceValues,"Reject")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="24" customHeight="1">
+      <c r="A19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="12">
+        <f>2+Interpolation_QueryX+3*Interpolation_QueryY+Interpolation_QueryX*Interpolation_QueryY</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="24" customHeight="1">
+      <c r="A20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="12">
+        <f>Interpolation_Bilinear-Interpolation_Analytic</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D3"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here"/>
+    <hyperlink ref="D4" location="'3 Schedules'!A1" display="Next → 3 Schedules"/>
+  </hyperlinks>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
+  <headerFooter>
+    <oddFooter>&amp;LQuantSupport&amp;CCompare native interpolation methods&amp;R&amp;P / &amp;N</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:L10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr>
+    <tabColor rgb="FF21845B"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
-    <col min="1" max="12" width="22.7109375" style="1" customWidth="1"/>
+    <col min="1" max="5" width="20.7109375" style="1" customWidth="1"/>
+    <col min="6" max="52" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3">
-      <c r="A2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" cm="1">
-        <f t="array" ref="A4">_xll.QS.SCHEDULE("2026-02-24","2027-02-24","Quarterly")</f>
-        <v>0</v>
-      </c>
-      <c r="C4" s="1" cm="1">
-        <f t="array" ref="C4">_xll.QS.SCHEDULE("2026-02-24","2027-02-24","Quarterly",TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="C8" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="C10" s="1" cm="1">
-        <f t="array" ref="C10">_xll.QS.SCHEDULE.ADJUSTED("2026-02-28","2027-02-28","Quarterly","TARGET","Following",TRUE)</f>
-        <v>0</v>
+    <row r="1" spans="1:5" ht="38" customHeight="1">
+      <c r="A1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" spans="1:5" ht="24" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:5" ht="24" customHeight="1">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" ht="24" customHeight="1">
+      <c r="A4" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="24" customHeight="1">
+      <c r="A6" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="24" customHeight="1">
+      <c r="A7" s="1" cm="1" t="str">
+        <f t="array" ref="A7">_xll.QS.SCHEDULE(Interpolation_Start,Interpolation_End,Interpolation_Frequency)</f>
+        <v/>
+      </c>
+      <c r="C7" s="1" cm="1" t="str">
+        <f t="array" ref="C7">_xll.QS.SCHEDULE.ADJUSTED(Interpolation_Start,Interpolation_End,Interpolation_Frequency,Interpolation_Calendar,Interpolation_Convention)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="24" customHeight="1">
+      <c r="A16" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:1" ht="24" customHeight="1">
+      <c r="A17" s="1" cm="1" t="str">
+        <f t="array" ref="A17">_xll.QS.SCHEDULE(Interpolation_Start,Interpolation_End,Interpolation_Frequency,TRUE)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E3"/>
+    <mergeCell ref="A16:E16"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here"/>
+  </hyperlinks>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
+  <headerFooter>
+    <oddFooter>&amp;LQuantSupport&amp;CThe same schedule in different layouts&amp;R&amp;P / &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>